--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.00846748557122654</v>
       </c>
       <c r="C2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31797936</v>
+        <v>4228629</v>
       </c>
       <c r="L2" t="n">
-        <v>18147857</v>
+        <v>2028946</v>
       </c>
       <c r="M2" t="n">
-        <v>4462884</v>
+        <v>432156</v>
       </c>
       <c r="N2" t="n">
-        <v>213535</v>
+        <v>11214</v>
       </c>
       <c r="O2" t="n">
-        <v>2652491</v>
+        <v>263362</v>
       </c>
       <c r="P2" t="n">
-        <v>1024179</v>
+        <v>102860</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999979555606842</v>
+        <v>0.9999970197677612</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8884755969047546</v>
+        <v>0.7937477231025696</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7781099677085876</v>
+        <v>0.6308370232582092</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7255694270133972</v>
+        <v>0.5243472456932068</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3725287914276123</v>
+        <v>0.1033262684941292</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7684974074363708</v>
+        <v>0.5851435661315918</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8545421361923218</v>
+        <v>0.7187327742576599</v>
       </c>
       <c r="X2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564294219017029</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113486409187317</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579833507537842</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620163917541504</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019670486450195</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029527753233312</v>
       </c>
       <c r="C3" t="n">
-        <v>567</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>31797936</v>
+        <v>4228629</v>
       </c>
       <c r="E3" t="n">
-        <v>3527426</v>
+        <v>781831</v>
       </c>
       <c r="F3" t="n">
-        <v>64640</v>
+        <v>23509</v>
       </c>
       <c r="G3" t="n">
-        <v>6033</v>
+        <v>1592</v>
       </c>
       <c r="H3" t="n">
-        <v>3846</v>
+        <v>1438</v>
       </c>
       <c r="I3" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="J3" t="n">
-        <v>70486432</v>
+        <v>10069601</v>
       </c>
       <c r="K3" t="n">
-        <v>75520009</v>
+        <v>10280149</v>
       </c>
       <c r="L3" t="n">
-        <v>86740226</v>
+        <v>11926791</v>
       </c>
       <c r="M3" t="n">
-        <v>106680475</v>
+        <v>15086898</v>
       </c>
       <c r="N3" t="n">
-        <v>113926612</v>
+        <v>16229049</v>
       </c>
       <c r="O3" t="n">
-        <v>110545653</v>
+        <v>15718819</v>
       </c>
       <c r="P3" t="n">
-        <v>113384135</v>
+        <v>16182240</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8982313275337219</v>
+        <v>0.8395037055015564</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7891527414321899</v>
+        <v>0.6144822239875793</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6820291876792908</v>
+        <v>0.4611735045909882</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3412634134292603</v>
+        <v>0.1251073777675629</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7435551285743713</v>
+        <v>0.5159286856651306</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7566714286804199</v>
+        <v>0.531557023525238</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1393396</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60111</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47831</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70487340</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77967120</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89879810</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107439825</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114074974</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110995151</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113465688</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575752019882202</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099511504173279</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573793172836304</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6614662408828735</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015187621116638</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03201304320695698</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3757100</v>
+        <v>1024602</v>
       </c>
       <c r="E4" t="n">
-        <v>18147857</v>
+        <v>2028946</v>
       </c>
       <c r="F4" t="n">
-        <v>967430</v>
+        <v>208997</v>
       </c>
       <c r="G4" t="n">
-        <v>39204</v>
+        <v>12357</v>
       </c>
       <c r="H4" t="n">
-        <v>78822</v>
+        <v>24609</v>
       </c>
       <c r="I4" t="n">
-        <v>6214</v>
+        <v>2364</v>
       </c>
       <c r="J4" t="n">
-        <v>908</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>3991383</v>
+        <v>1098793</v>
       </c>
       <c r="L4" t="n">
-        <v>5175140</v>
+        <v>1187330</v>
       </c>
       <c r="M4" t="n">
-        <v>1687987</v>
+        <v>392023</v>
       </c>
       <c r="N4" t="n">
-        <v>359669</v>
+        <v>97316</v>
       </c>
       <c r="O4" t="n">
-        <v>799038</v>
+        <v>186719</v>
       </c>
       <c r="P4" t="n">
-        <v>174333</v>
+        <v>40253</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999898076057434</v>
+        <v>0.9999985098838806</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8933268189430237</v>
+        <v>0.8159847855567932</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7835924625396729</v>
+        <v>0.6225522756576538</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7031258940696716</v>
+        <v>0.4907356202602386</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3562113642692566</v>
+        <v>0.1131784170866013</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7558205723762512</v>
+        <v>0.5483605861663818</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8026342988014221</v>
+        <v>0.6111342310905457</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1441845</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>581832</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38644</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8024</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1544272</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2035556</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>928637</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211307</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349540</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570019841194153</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106493592262268</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576812148094177</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617411971092224</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017428159713745</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>155516</v>
+        <v>52873</v>
       </c>
       <c r="E5" t="n">
-        <v>1402619</v>
+        <v>334742</v>
       </c>
       <c r="F5" t="n">
-        <v>4462884</v>
+        <v>432156</v>
       </c>
       <c r="G5" t="n">
-        <v>126385</v>
+        <v>30277</v>
       </c>
       <c r="H5" t="n">
-        <v>366004</v>
+        <v>77611</v>
       </c>
       <c r="I5" t="n">
-        <v>29957</v>
+        <v>9418</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3602672</v>
+        <v>808429</v>
       </c>
       <c r="L5" t="n">
-        <v>4848777</v>
+        <v>1272933</v>
       </c>
       <c r="M5" t="n">
-        <v>2080654</v>
+        <v>504923</v>
       </c>
       <c r="N5" t="n">
-        <v>412184</v>
+        <v>78421</v>
       </c>
       <c r="O5" t="n">
-        <v>914818</v>
+        <v>247100</v>
       </c>
       <c r="P5" t="n">
-        <v>329353</v>
+        <v>90647</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999920725822449</v>
+        <v>0.9999988675117493</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9339141845703125</v>
+        <v>0.8838193416595459</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9127687811851501</v>
+        <v>0.8501302003860474</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9672040939331055</v>
+        <v>0.9453614950180054</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9932830929756165</v>
+        <v>0.9892947673797607</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9850854873657227</v>
+        <v>0.9735733866691589</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9956167936325073</v>
+        <v>0.9920260906219482</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56517</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>598295</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69798</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204203</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1501863</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2070821</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>933244</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211827</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351313</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734916090965271</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642650485038757</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837973117828369</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963177442550659</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939009547233582</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383104801178</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>73921</v>
+        <v>18132</v>
       </c>
       <c r="E6" t="n">
-        <v>118826</v>
+        <v>21358</v>
       </c>
       <c r="F6" t="n">
-        <v>149835</v>
+        <v>27464</v>
       </c>
       <c r="G6" t="n">
-        <v>213535</v>
+        <v>11214</v>
       </c>
       <c r="H6" t="n">
-        <v>64381</v>
+        <v>10235</v>
       </c>
       <c r="I6" t="n">
-        <v>5149</v>
+        <v>1231</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45519</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37622</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76408</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48911</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>4627</v>
+        <v>3092</v>
       </c>
       <c r="E7" t="n">
-        <v>118561</v>
+        <v>45771</v>
       </c>
       <c r="F7" t="n">
-        <v>482405</v>
+        <v>122968</v>
       </c>
       <c r="G7" t="n">
-        <v>176361</v>
+        <v>48078</v>
       </c>
       <c r="H7" t="n">
-        <v>2652491</v>
+        <v>263362</v>
       </c>
       <c r="I7" t="n">
-        <v>132853</v>
+        <v>27185</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5676</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207971</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53175</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>7708</v>
+        <v>3628</v>
       </c>
       <c r="F8" t="n">
-        <v>23677</v>
+        <v>9085</v>
       </c>
       <c r="G8" t="n">
-        <v>11686</v>
+        <v>5012</v>
       </c>
       <c r="H8" t="n">
-        <v>285985</v>
+        <v>72826</v>
       </c>
       <c r="I8" t="n">
-        <v>1024179</v>
+        <v>102860</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
